--- a/www/download/COUNTRY.ROU.zdW13.xlsx
+++ b/www/download/COUNTRY.ROU.zdW13.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>Romênia</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.200944842620698</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.30565803346184</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.707018579958228</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.882526813020703</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.50713623441745</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.14389846899757</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.89620026258149</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.30480173923261</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.31928164503775</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.25701079222564</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.91002210893393</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.80465564467292</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.43463024937312</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.49929403971849</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.04146434603597</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>9.503</t>
+          <t>0.587142925095267</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>9.379</t>
+          <t>0.60966271538514</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>9.023</t>
+          <t>0.681959316478895</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>8.813</t>
+          <t>0.451252778159967</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>10.855</t>
+          <t>0.0868521935019906</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>10.771</t>
+          <t>-0.00650016396519126</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10.657</t>
+          <t>0.0228291366194389</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>9.574</t>
+          <t>0.372605852552688</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>9.569</t>
+          <t>0.748596665801427</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>0.620510965869712</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>9.267</t>
+          <t>0.438892684316792</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>9.331</t>
+          <t>0.489394858792249</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>9.365</t>
+          <t>0.452509065053673</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>9.366</t>
+          <t>0.384065556127337</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>9.212</t>
+          <t>0.536793408103705</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>5.814</t>
+          <t>1.18697514195576</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5.894</t>
+          <t>1.30057363023718</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>5.399</t>
+          <t>1.45997847089506</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>5.182</t>
+          <t>1.03585196307989</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>5.971</t>
+          <t>0.93861192006783</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5.882</t>
+          <t>0.657404153047789</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5.787</t>
+          <t>0.64775612514631</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>6.138</t>
+          <t>1.30259958989587</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>2.17706393965681</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>6.407</t>
+          <t>1.74738231689766</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>6.162</t>
+          <t>1.45012311463585</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>6.412</t>
+          <t>1.55017866595691</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>6.436</t>
+          <t>1.42490880379431</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>6.513</t>
+          <t>1.29063279760318</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>6.583</t>
+          <t>1.5826311117386</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>17008.077</t>
+          <t>2.06648514616398</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>17598.162</t>
+          <t>2.1289716279415</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>16800.278</t>
+          <t>2.49171767111458</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>16391.695</t>
+          <t>1.70675823240049</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20083.159</t>
+          <t>1.84102950222647</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>19959.764</t>
+          <t>1.38299779520619</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>19742.438</t>
+          <t>1.22681210841798</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>17876.156</t>
+          <t>2.04849515576797</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>17579.559</t>
+          <t>1.61761342785971</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>17371.251</t>
+          <t>2.70285378119809</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>17171.308</t>
+          <t>2.18446289376448</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>17305.201</t>
+          <t>2.4228937054666</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>17588.497</t>
+          <t>2.22772009548478</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>17593.169</t>
+          <t>1.98058322615893</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>17338.698</t>
+          <t>2.43354125126611</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>11128.807</t>
+          <t>25127068975.8773</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>11394.243</t>
+          <t>26445590539.1822</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>10468.573</t>
+          <t>23795639796.6386</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>10026.345</t>
+          <t>21840417036.3187</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>11606.427</t>
+          <t>27425519202.2057</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>11478.276</t>
+          <t>26596499241.1202</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>11318.912</t>
+          <t>25878662442.9065</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>11929.299</t>
+          <t>22076858663.7198</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>11555.4</t>
+          <t>21746261405.2019</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>12477.476</t>
+          <t>20917540453.8479</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>11991.971</t>
+          <t>20670088311.3483</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>12430.286</t>
+          <t>20674892760.6024</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>12497.741</t>
+          <t>20925586729.9547</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>12629.99</t>
+          <t>21040435084.518</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>12762.814</t>
+          <t>19903840111.4744</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>15.32</t>
+          <t>4136817853.90314</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>15.16</t>
+          <t>4130875542.40234</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>14.14</t>
+          <t>3438068233.18939</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>4122594515.73763</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>4864622455.9985</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>13.76</t>
+          <t>5664966264.23611</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>13.46</t>
+          <t>5837543521.66786</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>13.88</t>
+          <t>4518544496.17928</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>12.39</t>
+          <t>4506544636.7583</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>4032342072.63431</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>18.13</t>
+          <t>4488819497.41057</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>18.46</t>
+          <t>4407722005.31813</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>4664049474.53373</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>20.79</t>
+          <t>5094646327.6595</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>4570510512.25376</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>16.98</t>
+          <t>8868649.05285987</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>17.68</t>
+          <t>8443595.35652388</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>16.87</t>
+          <t>8302678.40077254</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>16.02</t>
+          <t>7437592.43592979</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>17.47</t>
+          <t>9330780.79267895</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>17.99</t>
+          <t>8799918.49540972</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>7687320.08998008</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>18.62</t>
+          <t>6581536.06557816</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>13.32</t>
+          <t>5184923.07376198</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>19.53</t>
+          <t>3882556.3213803</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>19.74</t>
+          <t>3157092.17135043</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>20.78</t>
+          <t>2685779.4396179</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>2008719.70581647</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>1689134.03133919</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>21.68</t>
+          <t>2021677.08488462</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>67.69</t>
+          <t>120799.76634796</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>67.16</t>
+          <t>124319.640285593</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>68.99</t>
+          <t>117393.818267882</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>70.87</t>
+          <t>112182.536568858</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>69.03</t>
+          <t>143027.889704432</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>68.25</t>
+          <t>143347.093747518</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>67.83</t>
+          <t>137397.139363348</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>67.5</t>
+          <t>122830.064144151</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>129503.289142183</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>63.28</t>
+          <t>134430.884389194</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>62.12</t>
+          <t>142156.467880755</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>60.76</t>
+          <t>148466.160116254</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>60.99</t>
+          <t>167797.007287164</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>59.46</t>
+          <t>183802.803462434</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>57.12</t>
+          <t>166481.192704643</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>7.85</t>
+          <t>216506.600398774</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>7.83</t>
+          <t>229498.623676676</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>7.26</t>
+          <t>205839.462784996</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>187020.359691098</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>244278.454235964</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6.99</t>
+          <t>240811.763094979</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>6.92</t>
+          <t>227559.406890578</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>7.24</t>
+          <t>198366.541613203</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>209471.470926225</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>9.22</t>
+          <t>221620.203643991</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>234560.180126535</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>244928.956666115</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>10.54</t>
+          <t>279317.453628889</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>11.51</t>
+          <t>307479.510827423</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>12.02</t>
+          <t>271149.182478735</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>14.94</t>
+          <t>1.69018552013262</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>15.58</t>
+          <t>1.75831189478294</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>14.84</t>
+          <t>2.04489973658919</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>14.1</t>
+          <t>1.43204734296871</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>15.27</t>
+          <t>1.3858844350168</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>15.68</t>
+          <t>1.02618611737625</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>16.31</t>
+          <t>0.938985458178828</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>16.24</t>
+          <t>1.64007558409284</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>16.65</t>
+          <t>1.56413747813495</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>17.58</t>
+          <t>2.09434958027966</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>1.67151998580422</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>18.72</t>
+          <t>1.82011569354925</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>1.67959014333771</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>18.44</t>
+          <t>1.47907100664282</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>20.22</t>
+          <t>1.79242627268658</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>77.21</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>76.59</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>79.18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>77.84</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>77.33</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>76.76</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.52</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>74.55</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>73.21</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>72.36</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>71.13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>71.26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>70.05</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>67.76</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.200944842620698</t>
+          <t>711.513909861591</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.30565803346184</t>
+          <t>700.859864951697</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.707018579958228</t>
+          <t>636.775666922458</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.882526813020703</t>
+          <t>795.606703162522</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.50713623441745</t>
+          <t>814.70816546617</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2.14389846899757</t>
+          <t>963.183926589494</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2.89620026258149</t>
+          <t>1008.7862722567</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>3.30480173923261</t>
+          <t>736.195072450475</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>3.31928164503775</t>
+          <t>763.782288486739</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>3.25701079222564</t>
+          <t>629.315969197708</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2.91002210893393</t>
+          <t>728.444305184929</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2.80465564467292</t>
+          <t>687.460541100213</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2.43463024937312</t>
+          <t>724.625102856168</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2.49929403971849</t>
+          <t>782.227288140566</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>3.04146434603597</t>
+          <t>694.28070222446</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>-1879429657.46196</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>-2053397138.97399</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>-2146904646.51119</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>-1810392963.2042</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>-2718866793.76847</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>-2511516055.36397</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>-2319325548.42477</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>-2492167543.11199</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>-2211145789.0593</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>-1954691762.72496</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>-1701451181.60908</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>-1544888284.84793</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>-1656656843.11204</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>-1633978620.86452</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>-1244863525.60908</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>-1882029900.74305</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>-2047355033.4615</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>-2167900949.65964</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>-1853555393.86698</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>-2793676541.64661</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>-2599770804.42799</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>-2425165309.95162</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>-2637291348.68075</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>-2425069893.49826</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>-2163708879.47998</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>-1951274689.19711</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-1892868168.12489</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>-1991019114.14281</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-2076363524.72751</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>-1723467975.71203</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>2600243.2810913</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>-6042105.51248645</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>20996303.1484517</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>43162430.6627873</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>74809747.8781341</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>88254749.0640255</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>105839761.526851</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.157</t>
+          <t>145123805.568758</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.194</t>
+          <t>213924104.438954</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>209017116.75502</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.297</t>
+          <t>249823507.588023</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.348</t>
+          <t>347979883.276958</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>334362271.030769</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.559</t>
+          <t>442384903.862996</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.489</t>
+          <t>478604450.102944</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>1914.1044176826</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>1933.19010207223</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>1938.9180604786</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>1934.9531684745</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>1943.79953106682</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>1951.58990053558</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>1956.02191231617</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>1943.61063590596</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.115</t>
+          <t>1958.44279104452</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>1947.32360515021</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>1946.05351984681</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.234</t>
+          <t>1938.71826065257</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.322</t>
+          <t>1941.69828322846</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.394</t>
+          <t>1939.19699063412</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.313</t>
+          <t>1938.72767351087</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>1789.74356910034</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>1876.36006753452</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>1862.02344960204</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>1860.05019838541</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>1850.06162831402</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>1853.03340327163</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>1852.46288963537</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>1867.1564654272</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>1837.04049323371</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>1846.00231663514</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>1852.89221240275</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>1854.59232665309</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>1878.12971841664</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>1878.34780009182</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>1882.18714064088</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>58.71</t>
+          <t>9015.42516999499</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>60.97</t>
+          <t>9424.89168999499</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>68.2</t>
+          <t>9716.80211999499</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>45.13</t>
+          <t>9329.596589995</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>8.69</t>
+          <t>9671.49620999501</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>11602.476589995</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>12503.776749996</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>37.26</t>
+          <t>14965.508649996</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>74.86</t>
+          <t>18960.547039996</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>62.05</t>
+          <t>25567.907739996</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>43.89</t>
+          <t>31153.799929996</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>48.94</t>
+          <t>38170.103819996</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>45.25</t>
+          <t>48894.796309996</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>38.41</t>
+          <t>60280.244599996</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>53.68</t>
+          <t>46893.386289996</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>118.7</t>
+          <t>2826542568.3373</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>130.06</t>
+          <t>2929233644.16162</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>2884674000.24993</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>103.59</t>
+          <t>2528566261.08373</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>93.86</t>
+          <t>3577522221.14599</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>65.74</t>
+          <t>3631601195.70428</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>64.78</t>
+          <t>3529424981.79585</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>130.26</t>
+          <t>3793277653.51628</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>217.71</t>
+          <t>3710230828.77825</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>174.74</t>
+          <t>3748656406.04437</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>145.01</t>
+          <t>3476219154.05623</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>155.02</t>
+          <t>3489631207.9898</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>142.49</t>
+          <t>3223166769.95541</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>129.06</t>
+          <t>3455613888.72559</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>158.26</t>
+          <t>3220219554.58982</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>206.65</t>
+          <t>10941.0688131599</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>212.9</t>
+          <t>12150.2883833094</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>249.17</t>
+          <t>11887.9487200439</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>170.68</t>
+          <t>12425.0202418549</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>184.1</t>
+          <t>11308.9760301437</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>138.3</t>
+          <t>13620.5575021578</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>122.68</t>
+          <t>15604.343044409</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>204.85</t>
+          <t>17610.5644620268</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>161.76</t>
+          <t>23491.8781941283</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>270.29</t>
+          <t>32323.2803527197</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>218.45</t>
+          <t>41395.4874568987</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>242.29</t>
+          <t>52856.4065527493</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>222.77</t>
+          <t>71798.6577295149</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>198.06</t>
+          <t>86273.899594741</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>243.35</t>
+          <t>56842.500007713</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>17008.077</t>
+          <t>1212503627.2505</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>17598.162</t>
+          <t>1236102421.03181</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>16800.278</t>
+          <t>1000495144.83884</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>16391.695</t>
+          <t>1115484411.00889</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20083.159</t>
+          <t>1073776764.12746</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>19959.764</t>
+          <t>1388527861.01288</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>19742.438</t>
+          <t>1644641882.70659</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>17876.156</t>
+          <t>1667700576.26374</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>17579.559</t>
+          <t>2095743953.89005</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>17371.251</t>
+          <t>2612016716.22471</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>17171.308</t>
+          <t>2923393195.4843</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>17305.201</t>
+          <t>3451228862.36805</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>17588.497</t>
+          <t>3645880843.81039</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>17593.169</t>
+          <t>3946180311.12846</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>17338.698</t>
+          <t>2870892996.77455</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>11128.807</t>
+          <t>-1925.6436431649</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>11394.243</t>
+          <t>-2725.39669331438</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>10468.573</t>
+          <t>-2171.14660004895</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>10026.345</t>
+          <t>-3095.4236518599</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>11606.427</t>
+          <t>-1637.47982014866</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>11478.276</t>
+          <t>-2018.08091216285</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>11318.912</t>
+          <t>-3100.56629441306</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>11929.299</t>
+          <t>-2645.05581203082</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>11555.4</t>
+          <t>-4531.33115413229</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>12477.476</t>
+          <t>-6755.37261272371</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>11991.971</t>
+          <t>-10241.6875269028</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>12430.286</t>
+          <t>-14686.3027327534</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>12497.741</t>
+          <t>-22903.8614195189</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>12629.99</t>
+          <t>-25993.654994745</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>12762.814</t>
+          <t>-9949.11371771708</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>25127.069</t>
+          <t>1614038941.0868</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>26445.591</t>
+          <t>1693131223.12981</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>23795.64</t>
+          <t>1884178855.41109</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>21840.417</t>
+          <t>1413081850.07484</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>27425.519</t>
+          <t>2503745457.01853</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>26596.499</t>
+          <t>2243073334.6914</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>25878.662</t>
+          <t>1884783099.08927</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>22076.859</t>
+          <t>2125577077.25255</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>21746.261</t>
+          <t>1614486874.8882</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>20917.54</t>
+          <t>1136639689.81965</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>20670.088</t>
+          <t>552825958.571924</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>20674.893</t>
+          <t>38402345.6217431</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>20925.587</t>
+          <t>-422714073.854985</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>21040.435</t>
+          <t>-490566422.402865</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>19903.84</t>
+          <t>349326557.815265</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.217</t>
+          <t>23336.75252</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>23380.70425</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.206</t>
+          <t>21982.16619</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.187</t>
+          <t>22614.83698</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.244</t>
+          <t>19009.69485</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.241</t>
+          <t>19167.23233</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.228</t>
+          <t>22411.43356</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.198</t>
+          <t>25121.62818</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>31505.19079</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>41573.58063</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>51146.00313</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.245</t>
+          <t>62791.13112</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.279</t>
+          <t>86627.44546</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.307</t>
+          <t>107462.62559</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.271</t>
+          <t>86061.9317</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>14019.638</t>
+          <t>0.111033495999886</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>14325.604</t>
+          <t>0.103921323956548</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>13571.066</t>
+          <t>0.121787210282457</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>13100.784</t>
+          <t>0.0853361103128969</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>16057.962</t>
+          <t>0.106797480235346</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>15831.996</t>
+          <t>0.0876438139266538</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>15625.169</t>
+          <t>0.067873669415328</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>13670.158</t>
+          <t>0.0776019126571169</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>13444.372</t>
+          <t>0.0769645117510742</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>12688.209</t>
+          <t>0.129348198543213</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>12527.219</t>
+          <t>0.104195685949652</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>12532.295</t>
+          <t>0.11043031045182</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>12570.825</t>
+          <t>0.121207070507028</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>12577.394</t>
+          <t>0.113255579483455</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>12220.634</t>
+          <t>0.113398372662094</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>14284.517009183</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>14117.410760155</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>11690.0745960578</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>16021.0430218163</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>12696.4634033637</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>14925.8000167552</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>16857.3288552141</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>18209.382789563</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>22301.843613053</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>28061.4360667414</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>38830.2546278648</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>47134.0930612798</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.168</t>
+          <t>66514.4530613812</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>86485.0219131855</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>66985.0361892292</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>4136.818</t>
+          <t>20953.9757959775</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>4130.876</t>
+          <t>20827.7154125453</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>3438.068</t>
+          <t>17878.2323324753</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>4122.595</t>
+          <t>25574.5068786929</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>4864.622</t>
+          <t>19246.946945127</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>5664.966</t>
+          <t>22387.8492687505</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>5837.544</t>
+          <t>26932.9122035333</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>4518.544</t>
+          <t>29223.1540073207</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>4506.545</t>
+          <t>38004.1607531317</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>4032.342</t>
+          <t>37815.7515167356</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>4488.819</t>
+          <t>56716.3153914071</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>4407.722</t>
+          <t>70036.737127413</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>4664.049</t>
+          <t>94380.2326877114</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>5094.646</t>
+          <t>120176.419878924</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>4570.511</t>
+          <t>91760.5600450726</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>169.02</t>
+          <t>134405.670555828</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>175.83</t>
+          <t>138291.398437762</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>204.49</t>
+          <t>128341.58407335</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>143.2</t>
+          <t>140767.682605421</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>138.59</t>
+          <t>125102.10611178</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>102.62</t>
+          <t>131661.510884344</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>93.9</t>
+          <t>143033.378187658</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>164.01</t>
+          <t>157317.857442779</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>156.41</t>
+          <t>193740.910292466</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>209.43</t>
+          <t>232061.861481868</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>167.15</t>
+          <t>297438.897168626</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>182.01</t>
+          <t>348189.400856234</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>167.96</t>
+          <t>469596.611271851</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>147.91</t>
+          <t>558820.926701643</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>179.24</t>
+          <t>489307.462464804</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>8.869</t>
+          <t>20953.9757959775</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>8.444</t>
+          <t>21595.0366867756</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>8.303</t>
+          <t>18568.8891500682</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>7.438</t>
+          <t>22952.3748023089</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>9.331</t>
+          <t>20618.1891217812</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>23217.9821996451</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>7.687</t>
+          <t>27580.3621459438</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>6.582</t>
+          <t>27991.1338055133</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>5.185</t>
+          <t>29848.6267121628</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>3.883</t>
+          <t>24378.2663766318</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>3.157</t>
+          <t>31500.6716348722</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2.686</t>
+          <t>34498.1691028764</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>2.009</t>
+          <t>35897.1168923718</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>1.689</t>
+          <t>39692.5976931957</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2.022</t>
+          <t>34014.9487228104</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>14284.517009183</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>14761.3062974795</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>12169.3016784859</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>13975.4343761728</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>12548.8282212418</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>14549.9339435519</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>16120.6752889863</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>15916.0977565602</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>16058.847195775</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>17122.527383603</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>19040.4391163132</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>20032.3729149732</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>21698.0059961549</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>24743.7870455706</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>21639.7454171529</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>14923.5314840225</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>14371.4252174547</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>15630.3634875247</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>12012.5664913071</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>13360.589704873</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>11539.3169612495</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>9708.20022646666</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>12208.1666326793</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>14911.1745668683</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>30016.7837332644</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>30991.8499185929</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>38450.663632587</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>56918.4295722886</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>63289.5878810759</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>55486.6699749274</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>11128807489.9963</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>11394243144.4763</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>10468573057.614</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>10026345038.1371</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>11606427000</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>11478276000</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>11318912000</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>11929299000</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>11555400000</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>12477476000</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>11991971000</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>12430286000</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>12497741000</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>12629990000</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>12762813634.0076</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>17008076566.2517</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>17598162191.4035</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>16800278404.2581</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>16391695466.7451</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>20083159000</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>19959764000</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>19742438000</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>17876156000</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>17579559000</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>17371251000</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>17171308000</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>17305201000</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>17588497000</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>17593169000</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>17338697861.6088</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>14019637533.9338</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>14325603571.388</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>13571066383.7692</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>13100784250.9917</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>16057962000</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>15831996000</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>15625169000</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>13670158000</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>13444372000</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>12688209000</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>12527219000</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>12532295000</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>12570825000</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>12577394000</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>12220634452.4776</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>9503080.13946449</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>9378883.34754797</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>9022592.28144989</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>8812501.66311301</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>10855400</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>10771400</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>10657400</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>9574000</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>9569500</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>9410200</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>9267300</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>9331000</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>9364900</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>9366300</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>9211994.64560414</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>5814106.78915309</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>5894010.69882498</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>5399182.80766852</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>5181699.07235622</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>5971000</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>5881500</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>5786700</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>6137700</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>5900300</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>6407500</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>6162200</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>6411600</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>6436500</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>6513000</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>6583087.35589215</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>17008076566.2517</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>17598162191.4035</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>16800278404.2581</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>16391695466.7451</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>20083159000</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>19959764000</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>19742438000</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>17876156000</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>17579559000</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>17371251000</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>17171308000</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>17305201000</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>17588497000</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>17593169000</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>17338697861.6088</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>11128807489.9963</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>11394243144.4763</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>10468573057.614</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>10026345038.1371</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>11606427000</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>11478276000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>11318912000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>11929299000</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>11555400000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>12477476000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>11991971000</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>12430286000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>12497741000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>12629990000</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>12762813634.0076</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.153249373821671</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.151591592079525</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.141357934736138</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.131085475404161</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.13503866866876</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.137628540907754</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.134641513454121</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.138774875738712</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.123858063604186</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.171829178515103</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.181345393421768</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.184575841473869</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.19112187778463</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.207927195251845</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.211989600542139</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.169808085044118</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.176824940679784</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.168692369777653</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.160217209274112</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.174665667557867</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.179910216418803</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.187035676667841</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.18621192661329</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.133184295915879</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.195344038586568</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.197423507628787</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.207830894374601</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.199025936164546</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.197474450575818</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.216775569682832</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.676942541134211</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.671583467240692</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.689949695486209</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.708697315321728</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.690295663773374</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.682461242673443</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.678322809878038</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.675013197647998</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.742957640479934</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.632826782898329</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.621231098949445</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.607593264151529</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.609852186050824</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.594598354172337</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.57123482977503</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.0785096043442988</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.0783260088229312</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.0725635829408859</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.0671800623138325</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.0688251783923756</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.0699078324120806</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.0692388796418979</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.0724385050920685</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.0880048178129122</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.0921735966508009</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.0974095903387319</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.101508629331494</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.105364824723641</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.115065358467651</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.120196730948339</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.149374382655247</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.155770502716519</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.148432965518307</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.141043625728438</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.152727722560584</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.156792418524991</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.163142546644421</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.162375411188584</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.16653267978683</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.175757286429952</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.179013652283156</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.187159780642293</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.182028895279162</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.18440883981998</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.202179913289584</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.772116013000455</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.76590348846055</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.779003451540807</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.79177631195773</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.77844709904704</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.773299749062929</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.767618573713681</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.765186083719348</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.745462502400258</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.732069116919247</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.723576757378112</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.711331590026213</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.712606279997197</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.700525801712369</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.677623355762077</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>79644.24419</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>82950.2155</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>76895.00852</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>80843.09454</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>72237.66396</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>73192.59749</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>78998.85387</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>89452.53788</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>115044.05127</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>148577.15376</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>188278.39696</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>234079.32454</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>322023.23116</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>394379.72946</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>312861.4044</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>35877.50728</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>35199.14063</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>33508.59582</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>37587.07337</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>32607.53665</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>33927.16623</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>36641.11243</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>41431.32064</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>52915.33532</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>67832.53525</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>87708.16531</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>108487.40076</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>151298.66226</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>183466.00776</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>147247.23002</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>27008.1262578989</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>27560.7777695561</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>28102.593183816</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>28512.4330760852</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>28817.1042268573</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>29192.1470307955</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>29694.9838785975</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>30317.3124995246</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>31062.735151797</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>31986.3200668522</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>33198.7943111179</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>34855.640122582</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>37358.6348316571</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>40334.0438289789</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>41909.9936147802</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>zdW13</t>
